--- a/ejemplos_briefing/03_operacionalidad_logistica.xlsx
+++ b/ejemplos_briefing/03_operacionalidad_logistica.xlsx
@@ -603,6 +603,31 @@
         <v>9</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BAE O'Higgins</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>30</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -610,10 +635,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1710</v>
+        <v>1740</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
